--- a/DataDriven_Framework/DataTables/DataDrivenResults.xlsx
+++ b/DataDriven_Framework/DataTables/DataDrivenResults.xlsx
@@ -3,12 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Analogfotography\DataDriven_Framework\DataTables\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7959699-66C7-40AD-93E5-4B80B078F650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{9CF37596-7323-4D88-A8A1-18A621B6151A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{D86A5495-945F-4A9E-A9C5-E194C0262502}"/>
   </bookViews>
@@ -16,6 +11,7 @@
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <oleSize ref="A1:P13"/>
   <extLst>
     <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t xml:space="preserve">Username </t>
   </si>
@@ -58,6 +54,9 @@
   </si>
   <si>
     <t>test456</t>
+  </si>
+  <si>
+    <t>Pass</t>
   </si>
   <si>
     <t>Fail</t>
@@ -126,7 +125,7 @@
       <b val="true"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -137,6 +136,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="17"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="17"/>
       </patternFill>
     </fill>
     <fill>
@@ -309,12 +318,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFill="true" applyFont="true"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFill="true" applyFont="true"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFill="true" applyFont="true"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFill="true" applyFont="true"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFill="true" applyFont="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -687,7 +696,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
@@ -698,7 +707,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s" s="12">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
@@ -720,7 +729,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
@@ -731,7 +740,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="s" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -742,7 +751,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="s" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
